--- a/data/inputs/horario_base.xlsx
+++ b/data/inputs/horario_base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D70902C8-C9A4-8D47-8353-F98A11CF9C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E548B85-5631-8546-B030-D44ABA9E7E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{B9482EA0-4DD2-F141-A14E-8B58C173E7AE}"/>
   </bookViews>

--- a/data/inputs/horario_base.xlsx
+++ b/data/inputs/horario_base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E548B85-5631-8546-B030-D44ABA9E7E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BD973E-9957-A842-A9EC-DA9DA6974073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{B9482EA0-4DD2-F141-A14E-8B58C173E7AE}"/>
   </bookViews>
